--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_160_R16.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_160_R16.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1997</v>
+        <v>3.6021</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9335</v>
+        <v>2.4367</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2662</v>
+        <v>1.1654</v>
       </c>
       <c r="G2" t="n">
         <v>1.4916</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2403</v>
+        <v>0.1621</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0376</v>
+        <v>-0.5344</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7973</v>
+        <v>0.6965</v>
       </c>
       <c r="V2" t="n">
         <v>0.7886</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1337</v>
+        <v>0.9595</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4159</v>
+        <v>2.3425</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2822</v>
+        <v>-1.383</v>
       </c>
       <c r="G3" t="n">
         <v>0.8013</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5643</v>
+        <v>0.3901</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6122</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0479</v>
+        <v>-0.1487</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3071</v>
+        <v>0.2147</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.446</v>
+        <v>1.0048</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7531</v>
+        <v>-0.79</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2745</v>
+        <v>-0.149</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.365</v>
+        <v>-0.5137</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.3647</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5817</v>
+        <v>0.9771</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.729</v>
+        <v>0.0336</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1472</v>
+        <v>0.9435</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3072</v>
+        <v>-1.1261</v>
       </c>
       <c r="N4" t="n">
-        <v>0.364</v>
+        <v>-0.5473</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0568</v>
+        <v>-0.5788</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2801</v>
+        <v>0.3637</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6176</v>
+        <v>0.0277</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6625</v>
+        <v>0.3361</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2228</v>
+        <v>-0.2005</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7689</v>
+        <v>-0.8864</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9917</v>
+        <v>0.6859</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.149</v>
+        <v>-0.2745</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5137</v>
+        <v>-0.365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3647</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9771</v>
+        <v>-0.5817</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0336</v>
+        <v>-0.729</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9435</v>
+        <v>0.1472</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1261</v>
+        <v>0.3072</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5473</v>
+        <v>0.364</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5788</v>
+        <v>-0.0568</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0738</v>
+        <v>0.7725</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2082</v>
+        <v>0.1772</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1344</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1111</v>
+        <v>-1.0103</v>
       </c>
       <c r="E6" t="n">
         <v>-0.9568</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1543</v>
+        <v>-0.0535</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9543</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1568</v>
+        <v>-0.056</v>
       </c>
       <c r="T6" t="n">
         <v>-0.224</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8642</v>
+        <v>-1.5986</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8705</v>
+        <v>-1.3353</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0064</v>
+        <v>-0.2633</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.229</v>
+        <v>-1.0165</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9052</v>
+        <v>-0.3206</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1343</v>
+        <v>-0.6959</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1107</v>
+        <v>-0.044</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8234</v>
+        <v>-0.1912</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7127</v>
+        <v>0.1472</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3398</v>
+        <v>-0.9725</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0818</v>
+        <v>-0.1294</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4216</v>
+        <v>-0.8431</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4933</v>
+        <v>-0.0255</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8215</v>
+        <v>-0.6445</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3282</v>
+        <v>0.619</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.7886</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6468</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.32</v>
+        <v>-1.6215</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7205</v>
+        <v>-1.7959</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5994</v>
+        <v>0.1744</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0165</v>
+        <v>-0.229</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3206</v>
+        <v>0.9052</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6959</v>
+        <v>-1.1343</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.044</v>
+        <v>0.1107</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1912</v>
+        <v>0.8234</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1472</v>
+        <v>-0.7127</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9725</v>
+        <v>-0.3398</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1294</v>
+        <v>0.0818</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8431</v>
+        <v>-0.4216</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
+        <v>-0.2506</v>
+      </c>
+      <c r="T8" t="n">
         <v>-0.7468</v>
       </c>
-      <c r="T8" t="n">
-        <v>-1.0297</v>
-      </c>
       <c r="U8" t="n">
-        <v>0.2829</v>
+        <v>0.4962</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7886</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6468</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0873</v>
+        <v>-2.6541</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0628</v>
+        <v>-2.7641</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0245</v>
+        <v>0.11</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7985</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2012</v>
+        <v>0.232</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4674</v>
+        <v>-0.1687</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2662</v>
+        <v>0.4007</v>
       </c>
       <c r="V9" t="n">
         <v>0.5361</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3396</v>
+        <v>-3.315</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5941</v>
+        <v>-4.4015</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2545</v>
+        <v>1.0864</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7555</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4424</v>
+        <v>-0.4178</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8215</v>
+        <v>-0.6289</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3791</v>
+        <v>0.2111</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0626</v>
+        <v>-3.6415</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1332</v>
+        <v>0.2207</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.9294</v>
+        <v>-3.8622</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6539</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3365</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>0.1298</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.502</v>
+        <v>-4.6715</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3132</v>
+        <v>-2.0459</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1887</v>
+        <v>-2.6256</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8983</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3062</v>
+        <v>0.1366</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8962</v>
+        <v>-0.6289</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2024</v>
+        <v>0.7655</v>
       </c>
       <c r="V12" t="n">
         <v>-1.214</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5264</v>
+        <v>-4.9649</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0728</v>
+        <v>-3.377</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4536</v>
+        <v>-1.588</v>
       </c>
       <c r="G13" t="n">
         <v>-2.4827</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.42</v>
+        <v>0.1415</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6642</v>
+        <v>0.0316</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2443</v>
+        <v>0.1098</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5361</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-20.3955</v>
+        <v>-18.9016</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.0516</v>
+        <v>-11.5582</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.343599999999999</v>
+        <v>-7.3435</v>
       </c>
       <c r="G14" t="n">
         <v>-12.9193</v>
@@ -1546,13 +1546,13 @@
         <v>6.9588</v>
       </c>
       <c r="S14" t="n">
-        <v>0.03949999999999992</v>
+        <v>1.5332</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.1645</v>
+        <v>-2.6711</v>
       </c>
       <c r="U14" t="n">
-        <v>4.2041</v>
+        <v>4.2043</v>
       </c>
       <c r="V14" t="n">
         <v>-4.0363</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.1982</v>
+        <v>7.715</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9617</v>
+        <v>4.1976</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2365</v>
+        <v>3.5175</v>
       </c>
       <c r="G15" t="n">
         <v>5.4842</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7499</v>
+        <v>-0.233</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2617</v>
+        <v>-1.0258</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5118</v>
+        <v>0.7927</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. POIRIER</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.794</v>
+        <v>4.4593</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6953</v>
+        <v>4.4563</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0987</v>
+        <v>0.0031</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1182</v>
+        <v>3.5575</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.0686</v>
+        <v>0.3554</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9504</v>
+        <v>3.202</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.0437</v>
+        <v>3.2395</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.2645</v>
+        <v>0.1379</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2208</v>
+        <v>3.1015</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9255</v>
+        <v>0.318</v>
       </c>
       <c r="N16" t="n">
-        <v>0.196</v>
+        <v>0.2175</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7296</v>
+        <v>0.1005</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0925</v>
+        <v>-0.7244</v>
       </c>
       <c r="T16" t="n">
-        <v>0.311</v>
+        <v>-0.9276</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7815</v>
+        <v>0.2032</v>
       </c>
       <c r="V16" t="n">
-        <v>2.428</v>
+        <v>0.9304</v>
       </c>
       <c r="W16" t="n">
-        <v>2.428</v>
+        <v>2.1444</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>V. POIRIER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7916</v>
+        <v>3.418</v>
       </c>
       <c r="E17" t="n">
-        <v>4.3383</v>
+        <v>0.1055</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5467</v>
+        <v>3.3125</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5575</v>
+        <v>-1.1182</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3554</v>
+        <v>-2.0686</v>
       </c>
       <c r="I17" t="n">
-        <v>3.202</v>
+        <v>0.9504</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2395</v>
+        <v>-2.0437</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1379</v>
+        <v>-2.2645</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1015</v>
+        <v>0.2208</v>
       </c>
       <c r="M17" t="n">
-        <v>0.318</v>
+        <v>0.9255</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2175</v>
+        <v>0.196</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1005</v>
+        <v>0.7296</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3921</v>
+        <v>0.7165</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0455</v>
+        <v>-0.2787</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3466</v>
+        <v>0.9952</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9304</v>
+        <v>2.428</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1444</v>
+        <v>2.428</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2823</v>
+        <v>2.3159</v>
       </c>
       <c r="E18" t="n">
         <v>1.8393</v>
       </c>
       <c r="F18" t="n">
-        <v>0.443</v>
+        <v>0.4766</v>
       </c>
       <c r="G18" t="n">
         <v>1.5459</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0523</v>
+        <v>-0.0187</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V18" t="n">
         <v>0.7886</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1621</v>
+        <v>2.112</v>
       </c>
       <c r="E19" t="n">
-        <v>2.211</v>
+        <v>2.329</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.049</v>
+        <v>-0.217</v>
       </c>
       <c r="G19" t="n">
         <v>2.3029</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0215</v>
+        <v>-0.0286</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3203</v>
+        <v>0.1522</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3943</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7094</v>
+        <v>1.0861</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5177</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1917</v>
+        <v>1.1581</v>
       </c>
       <c r="G20" t="n">
         <v>0.2289</v>
@@ -2014,13 +2014,13 @@
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>1.625</v>
+        <v>1.0016</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6097</v>
+        <v>0.02</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0152</v>
+        <v>0.9816</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>R. BEAUBOIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0834</v>
+        <v>0.9354</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2676</v>
+        <v>0.7557</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8158</v>
+        <v>0.1797</v>
       </c>
       <c r="G21" t="n">
-        <v>0.139</v>
+        <v>1.1374</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1189</v>
+        <v>2.5293</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0201</v>
+        <v>-1.3919</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3929</v>
+        <v>0.7659</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3193</v>
+        <v>2.1545</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0736</v>
+        <v>-1.3887</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2539</v>
+        <v>0.3715</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2004</v>
+        <v>0.3748</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0535</v>
+        <v>-0.0033</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0345</v>
+        <v>-0.3618</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1246</v>
+        <v>-0.5463</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0901</v>
+        <v>0.1845</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. BEAUBOIS</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6373</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6377</v>
+        <v>-1.7503</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0004</v>
+        <v>2.6005</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1374</v>
+        <v>1.2098</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5293</v>
+        <v>-3.2906</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3919</v>
+        <v>4.5004</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7659</v>
+        <v>1.0275</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1545</v>
+        <v>-3.0579</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3887</v>
+        <v>4.0854</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3715</v>
+        <v>0.1823</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3748</v>
+        <v>-0.2327</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0033</v>
+        <v>0.415</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.7834</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6598000000000001</v>
+        <v>0.6379</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6642</v>
+        <v>-0.5305</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0044</v>
+        <v>1.1683</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
       <c r="W22" t="n">
         <v>0.5361</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4957</v>
+        <v>0.5944</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.34</v>
+        <v>-0.3222</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8358</v>
+        <v>0.9166</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2098</v>
+        <v>0.139</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.2906</v>
+        <v>0.1189</v>
       </c>
       <c r="I23" t="n">
-        <v>4.5004</v>
+        <v>0.0201</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0275</v>
+        <v>0.3929</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.0579</v>
+        <v>0.3193</v>
       </c>
       <c r="L23" t="n">
-        <v>4.0854</v>
+        <v>0.0736</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1823</v>
+        <v>-0.2539</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2327</v>
+        <v>-0.2004</v>
       </c>
       <c r="O23" t="n">
-        <v>0.415</v>
+        <v>-0.0535</v>
       </c>
       <c r="P23" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-1.3917</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-2.7834</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2834</v>
+        <v>0.5456</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1202</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4036</v>
+        <v>0.0108</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.0913</v>
+        <v>-0.2999</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0511</v>
+        <v>-1.4613</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9598</v>
+        <v>1.1614</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3062</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2311</v>
+        <v>0.5603</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8136</v>
+        <v>-0.2238</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5825</v>
+        <v>0.7842</v>
       </c>
       <c r="V24" t="n">
         <v>0.1418</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.6674</v>
+        <v>-1.2184</v>
       </c>
       <c r="E25" t="n">
         <v>-2.7338</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0664</v>
+        <v>1.5154</v>
       </c>
       <c r="G25" t="n">
         <v>-1.2618</v>
@@ -2404,13 +2404,13 @@
         <v>0.6959</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0113</v>
+        <v>-0.5623</v>
       </c>
       <c r="T25" t="n">
         <v>-0.9709</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0404</v>
+        <v>0.4086</v>
       </c>
       <c r="V25" t="n">
         <v>0.1418</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>20.3953</v>
+        <v>21.9681</v>
       </c>
       <c r="E26" t="n">
-        <v>7.3437</v>
+        <v>7.3438</v>
       </c>
       <c r="F26" t="n">
-        <v>13.0516</v>
+        <v>14.6244</v>
       </c>
       <c r="G26" t="n">
         <v>12.9194</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7326000000000003</v>
+        <v>-0.7325999999999998</v>
       </c>
       <c r="I26" t="n">
         <v>13.6517</v>
@@ -2473,7 +2473,7 @@
         <v>2.0589</v>
       </c>
       <c r="P26" t="n">
-        <v>3.479299999999999</v>
+        <v>3.4793</v>
       </c>
       <c r="Q26" t="n">
         <v>-6.9586</v>
@@ -2482,19 +2482,19 @@
         <v>10.438</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.03960000000000019</v>
+        <v>1.5331</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.2042</v>
+        <v>-4.2043</v>
       </c>
       <c r="U26" t="n">
-        <v>4.1646</v>
+        <v>5.737299999999999</v>
       </c>
       <c r="V26" t="n">
         <v>4.0363</v>
       </c>
       <c r="W26" t="n">
-        <v>8.356200000000001</v>
+        <v>8.356199999999999</v>
       </c>
       <c r="X26" t="n">
         <v>-4.319900000000001</v>
